--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.18775896063519</v>
+        <v>0.6805108311032183</v>
       </c>
       <c r="D2" t="n">
-        <v>4.88694261280083</v>
+        <v>0.7941281745801348</v>
       </c>
       <c r="E2" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F2" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.773692748069</v>
+        <v>5.163225071561213</v>
       </c>
       <c r="D3" t="n">
-        <v>31.66854030254472</v>
+        <v>5.146137799163516</v>
       </c>
       <c r="E3" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F3" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.59984455833327</v>
+        <v>6.109974740729156</v>
       </c>
       <c r="D4" t="n">
-        <v>37.44038707951321</v>
+        <v>6.084062900420896</v>
       </c>
       <c r="E4" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F4" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.13251821145496</v>
+        <v>2.621534209361432</v>
       </c>
       <c r="D5" t="n">
-        <v>15.91867435988454</v>
+        <v>2.586784583481238</v>
       </c>
       <c r="E5" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F5" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.63009326999208</v>
+        <v>4.977390156373713</v>
       </c>
       <c r="D6" t="n">
-        <v>30.89776291643342</v>
+        <v>5.020886473920431</v>
       </c>
       <c r="E6" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F6" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.48007883336291</v>
+        <v>3.978012810421472</v>
       </c>
       <c r="D7" t="n">
-        <v>24.57710006840743</v>
+        <v>3.993778761116208</v>
       </c>
       <c r="E7" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F7" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.6024838457666</v>
+        <v>7.085403624937072</v>
       </c>
       <c r="D8" t="n">
-        <v>43.79209068543094</v>
+        <v>7.116214736382527</v>
       </c>
       <c r="E8" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F8" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.53075409116867</v>
+        <v>6.098747539814909</v>
       </c>
       <c r="D9" t="n">
-        <v>37.24865082873971</v>
+        <v>6.052905759670203</v>
       </c>
       <c r="E9" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F9" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.34315480744166</v>
+        <v>5.255762656209271</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9868962334905</v>
+        <v>5.197870637942206</v>
       </c>
       <c r="E10" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F10" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.4543006628181</v>
+        <v>3.648823857707941</v>
       </c>
       <c r="D11" t="n">
-        <v>21.31956323528509</v>
+        <v>3.464429025733827</v>
       </c>
       <c r="E11" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F11" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.28720450781125</v>
+        <v>2.321670732519328</v>
       </c>
       <c r="D12" t="n">
-        <v>13.47829362690138</v>
+        <v>2.190222714371475</v>
       </c>
       <c r="E12" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F12" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.06116532985656</v>
+        <v>3.097439366101691</v>
       </c>
       <c r="D13" t="n">
-        <v>18.82925338395636</v>
+        <v>3.059753674892909</v>
       </c>
       <c r="E13" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F13" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.00884271395179</v>
+        <v>3.251436941017166</v>
       </c>
       <c r="D14" t="n">
-        <v>20.38100115693562</v>
+        <v>3.311912688002038</v>
       </c>
       <c r="E14" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F14" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>15.99626342597149</v>
+        <v>2.599392806720368</v>
       </c>
       <c r="D15" t="n">
-        <v>15.2466783215765</v>
+        <v>2.477585227256181</v>
       </c>
       <c r="E15" t="n">
-        <v>10.58258575830146</v>
+        <v>1.719670185723987</v>
       </c>
       <c r="F15" t="n">
-        <v>10.60201536036274</v>
+        <v>1.722827496058945</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
